--- a/benchmarks/attachment_intelligence/fixtures/files/f27.xlsx
+++ b/benchmarks/attachment_intelligence/fixtures/files/f27.xlsx
@@ -60,12 +60,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit price, USD</t>
+          <t xml:space="preserve">Price, USD</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amount, USD</t>
+          <t xml:space="preserve">Amount</t>
         </is>
       </c>
     </row>
